--- a/meanchey-grilled-chicken-ui/public/templates/delivery_note_template.xlsx
+++ b/meanchey-grilled-chicken-ui/public/templates/delivery_note_template.xlsx
@@ -85,11 +85,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="[$-409]dd\-mmm\-yy;@"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="[$-409]d\-mmm\-yy;@"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -252,11 +253,11 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -576,7 +577,7 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.1796875" style="2"/>
     <col min="2" max="2" width="12.81640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="32.81640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="5.36328125" style="2" customWidth="1"/>
@@ -689,7 +690,7 @@
       <c r="C13" s="7"/>
       <c r="D13" s="6"/>
       <c r="E13" s="21"/>
-      <c r="F13" s="22"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
@@ -699,7 +700,7 @@
       <c r="C14" s="7"/>
       <c r="D14" s="6"/>
       <c r="E14" s="21"/>
-      <c r="F14" s="22"/>
+      <c r="F14" s="23"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
@@ -734,7 +735,7 @@
       <c r="A24" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="23"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="15"/>
       <c r="D24" s="15" t="s">
         <v>19</v>
